--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 86 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2799,8 +2799,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4383,8 +4383,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -9083,13 +9083,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -16016,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -18669,7 +18669,7 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q180" s="9" t="n">
         <v>0</v>
@@ -21130,7 +21130,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21229,7 +21229,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,11 @@
       <c r="AB138" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -15227,7 +15231,11 @@
       <c r="AB146" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -16560,7 +16568,11 @@
       <c r="AB159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2373,8 +2373,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P17" s="9" t="n">
-        <v>3</v>
+      <c r="P17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2502,8 +2502,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2574,8 +2574,8 @@
       <c r="P19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>1</v>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="10" t="n">
         <v>2</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6561,8 +6561,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7155,8 +7155,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7751,8 +7751,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8842,8 +8842,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8984,13 +8984,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9040,8 +9040,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9281,13 +9281,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9325,8 +9325,8 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>3</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9578,13 +9578,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9622,8 +9622,8 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10030,8 +10030,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10073,13 +10073,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10723,8 +10723,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>1</v>
@@ -15467,7 +15467,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15537,8 +15537,8 @@
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -16530,7 +16530,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>1</v>
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18508,8 +18508,8 @@
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="9" t="n">
-        <v>0</v>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
@@ -19159,13 +19159,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>1</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -21142,7 +21142,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21373,7 +21373,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21406,7 +21406,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21472,7 +21472,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21538,7 +21538,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21571,7 +21571,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21604,13 +21604,13 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -21637,7 +21637,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21967,7 +21967,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22132,7 +22132,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -1995,8 +1995,8 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>3</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2889,8 +2889,8 @@
       <c r="V22" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>3</v>
+      <c r="W22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3669,8 +3669,8 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>1</v>
+      <c r="S30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>0</v>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4426,13 +4426,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4624,13 +4624,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
         <v>2</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5119,13 +5119,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7495,13 +7495,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7539,8 +7539,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>3</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -8321,7 +8321,7 @@
         <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8416,8 +8416,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P78" s="9" t="n">
-        <v>3</v>
+      <c r="P78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q78" s="10" t="n">
         <v>2</v>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8489,13 +8489,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8533,8 +8533,8 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>1</v>
@@ -9281,17 +9281,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10667,17 +10667,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -11198,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -11459,17 +11459,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L109" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="7" t="n">
@@ -11657,13 +11657,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11756,13 +11756,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -11791,11 +11791,11 @@
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="S112" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -13538,13 +13538,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13740,13 +13740,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L132" s="8" t="inlineStr">
         <is>
@@ -13784,8 +13784,8 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>3</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13942,13 +13942,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14174,13 +14174,13 @@
         <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S136" s="9" t="n">
-        <v>0</v>
+      <c r="S136" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T136" s="9" t="n">
         <v>0</v>
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X140" s="10" t="n">
         <v>7</v>
@@ -15469,13 +15469,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149" s="8" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15679,13 +15679,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" s="8" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>5</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16907,13 +16907,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16951,8 +16951,8 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>3</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -17012,13 +17012,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X164" s="10" t="n">
         <v>4</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17758,8 +17758,8 @@
       <c r="P171" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" s="9" t="n">
-        <v>1</v>
+      <c r="Q171" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>1</v>
@@ -18377,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="Q177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
@@ -19795,7 +19795,7 @@
         <v>0</v>
       </c>
       <c r="Q191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
@@ -20076,13 +20076,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L194" s="8" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>0</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
@@ -20264,7 +20264,7 @@
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20316,8 +20316,8 @@
       <c r="S196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T196" s="9" t="n">
-        <v>0</v>
+      <c r="T196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U196" s="9" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -20480,13 +20480,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L198" s="8" t="inlineStr">
         <is>
@@ -20524,8 +20524,8 @@
       <c r="U198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="9" t="n">
-        <v>2</v>
+      <c r="V198" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21373,13 +21373,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -21406,7 +21406,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21637,7 +21637,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -21703,7 +21703,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -21784,7 +21784,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -21850,7 +21850,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -21901,7 +21901,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21916,7 +21916,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -22033,7 +22033,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22066,7 +22066,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22231,7 +22231,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22297,7 +22297,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22462,7 +22462,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/72/inyear.xlsx
+++ b/docs/d/72/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1456,17 +1456,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1504,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8" s="9" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2149,17 +2149,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2679,8 +2679,8 @@
       <c r="R20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="9" t="n">
-        <v>1</v>
+      <c r="S20" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T20" s="9" t="n">
         <v>0</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>2</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7140,8 +7140,8 @@
       <c r="T65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
+      <c r="U65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V65" s="9" t="n">
         <v>2</v>
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="9" t="n">
         <v>0</v>
@@ -7794,13 +7794,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8489,13 +8489,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>5</v>
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9112,8 +9112,8 @@
       <c r="P85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" s="9" t="n">
-        <v>1</v>
+      <c r="Q85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10076,10 +10076,10 @@
         <v>16</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11162,13 +11162,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11884,8 +11884,8 @@
       <c r="P113" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" s="9" t="n">
-        <v>1</v>
+      <c r="Q113" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12633,7 +12633,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12694,8 +12694,8 @@
       <c r="V121" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W121" s="9" t="n">
-        <v>3</v>
+      <c r="W121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>5</v>
@@ -12944,13 +12944,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>7</v>
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>6</v>
@@ -13524,7 +13524,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13538,13 +13538,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -13582,8 +13582,8 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>3</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13677,8 +13677,8 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
@@ -14043,13 +14043,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14085,10 +14085,10 @@
         <v>1</v>
       </c>
       <c r="U135" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14245,13 +14245,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L137" s="8" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="9" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14574,8 +14574,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P140" s="9" t="n">
-        <v>3</v>
+      <c r="P140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>1</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" s="10" t="n">
         <v>1</v>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>1</v>
@@ -15807,7 +15807,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -15881,13 +15881,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L153" s="8" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16233,8 +16233,8 @@
       <c r="T156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
+      <c r="U156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V156" s="9" t="n">
         <v>2</v>
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>6</v>
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -19343,7 +19343,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19392,8 +19392,8 @@
       <c r="R187" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S187" s="9" t="n">
-        <v>1</v>
+      <c r="S187" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T187" s="10" t="n">
         <v>1</v>
@@ -20466,7 +20466,7 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -20518,8 +20518,8 @@
       <c r="S198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T198" s="9" t="n">
-        <v>0</v>
+      <c r="T198" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U198" s="9" t="n">
         <v>0</v>
@@ -21289,7 +21289,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -21322,7 +21322,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -21340,7 +21340,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21604,7 +21604,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21736,7 +21736,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -21901,7 +21901,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21967,13 +21967,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -22033,7 +22033,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22099,7 +22099,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -22198,7 +22198,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22396,13 +22396,13 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -22462,7 +22462,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
